--- a/Insurance Rate Data Scraper/output/va_all_companies_search.xlsx
+++ b/Insurance Rate Data Scraper/output/va_all_companies_search.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1104"/>
+  <dimension ref="A1:AG1225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73368,6 +73368,7721 @@
         </is>
       </c>
     </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>SFMA-134997212</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>134997212</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>PV-50027</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1105" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1105" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1105" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1105" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134997212</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>SFMA-134969889</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>134969889</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>PV-50513</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1106" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1106" t="inlineStr">
+        <is>
+          <t>Closed - Withdrawn</t>
+        </is>
+      </c>
+      <c r="P1106" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1106" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1106" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134969889</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>SFMA-135040428</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>135040428</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>PV-50846</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1107" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1107" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1107" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1107" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1107" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135040428</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>SFMA-134963773</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>134963773</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>25143</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>CL-50242</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>05.0000 CMP Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1108" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1108" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1108" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1108" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134963773</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>SFMA-134987642</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>134987642</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>25143</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>CM-50622</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>09.0005 Other Commercial Inland Marine</t>
+        </is>
+      </c>
+      <c r="J1109" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1109" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1109" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1109" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134987642</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>GECC-134851213</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>134851213</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>083 - Cycle Rate/Rule</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="J1110" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1110" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1110" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1110" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134851213</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>GECC-134956225</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>134956225</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>083A - Cycle Forms</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="J1111" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1111" t="inlineStr">
+        <is>
+          <t>Closed - Disapproved and Returned to Company</t>
+        </is>
+      </c>
+      <c r="P1111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1111" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1111" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134956225</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>GECC-134953474</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>134953474</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>193 - Auto Forms Informational Filing</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1112" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1112" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1112" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1112" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134953474</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>GECC-135017634</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>135017634</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>257 - Comm Rate</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>20.0001 Business Auto</t>
+        </is>
+      </c>
+      <c r="J1113" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1113" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1113" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1113" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135017634</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>PRGS-134898215</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>134898215</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>VA 202601</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1114" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1114" t="inlineStr">
+        <is>
+          <t>Pending Response</t>
+        </is>
+      </c>
+      <c r="P1114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1114" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1114" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134898215</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>PRGS-134930548</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>134930548</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>38628</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>Businessowners</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1115" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1115" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P1115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1115" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1115" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134930548</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>PRGS-134986710</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>134986710</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>38628</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>Commercial Auto Program</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>17.1001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1116" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1116" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1116" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134986710</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>PRGS-134986700</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>134986700</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>38628</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>Commercial Auto Program</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>20.0001 Business Auto</t>
+        </is>
+      </c>
+      <c r="J1117" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1117" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1117" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1117" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134986700</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>ALSE-134982424</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>134982424</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>Allstate</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>29688</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>AFCIC PPA</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1118" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1118" t="inlineStr">
+        <is>
+          <t>Closed - Receipt Acknowledged</t>
+        </is>
+      </c>
+      <c r="P1118" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1118" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1118" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134982424</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>ALSE-134941113</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>134941113</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>Allstate</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>11110</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>ANAIC LL&amp;H</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1119" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1119" t="inlineStr">
+        <is>
+          <t>Pending - Other</t>
+        </is>
+      </c>
+      <c r="P1119" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1119" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1119" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134941113</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>ALSE-134970309</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>134970309</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Allstate</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>11110</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>ANAIC PPA</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1120" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1120" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1120" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1120" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1120" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134970309</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>ALSE-135017915</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>135017915</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>Allstate</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>AIC AI REN</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>04.0004 Tenant Homeowners</t>
+        </is>
+      </c>
+      <c r="J1121" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1121" t="inlineStr">
+        <is>
+          <t>Pending Response</t>
+        </is>
+      </c>
+      <c r="P1121" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1121" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1121" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135017915</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>ALSE-134994322</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>134994322</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>Allstate</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>APC AIC BO</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>09.0010 Boatowners/Personal Watercraft</t>
+        </is>
+      </c>
+      <c r="J1122" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1122" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P1122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1122" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1122" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134994322</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>TRVD-G135018490</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>135023434</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>Bill Plan</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>35.0001 Personal Interline Filings</t>
+        </is>
+      </c>
+      <c r="J1123" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1123" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1123" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1123" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135023434</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>TRVD-134916680</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>134916680</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>CLM Div. 6 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1124" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1124" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1124" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1124" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134916680</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>TRVD-135033559</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>135033559</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>CLM Div. 6 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1125" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1125" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1125" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1125" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135033559</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>TRVD-134946275</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>134946275</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>CLM-Div-1-Commercial Auto</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>20.0000 Commercial Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1126" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1126" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1126" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1126" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134946275</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>TRVD-134932453</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>134932453</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>CLM-Div-1-Commercial Auto</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>20.0000 Commercial Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1127" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1127" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1127" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1127" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134932453</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>TRVD-134946235</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>134946235</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>CLM-Div-1-Commercial Auto</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>20.0000 Commercial Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1128" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1128" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1128" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1128" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134946235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>TRVD-134940156</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>134940156</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>CLM-Div-1-Commercial Auto</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>20.0000 Commercial Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1129" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1129" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1129" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1129" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134940156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>TRVD-134987024</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>134987024</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>17.1001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1130" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1130" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P1130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1130" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1130" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134987024</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>TRVD-G135009170</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>135009596</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>Legacy Homeowners</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1131" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1131" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1131" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1131" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1131" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135009596</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>TRVD-135020197</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>135020197</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>OMNI II General Liability</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1132" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1132" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1132" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1132" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135020197</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>TRVD-G134961703</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>134971050</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>Credit Union Bond Rate/Form Filing 2026-03-0740</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>23.0000 Fidelity</t>
+        </is>
+      </c>
+      <c r="J1133" t="inlineStr">
+        <is>
+          <t>Form/Rate</t>
+        </is>
+      </c>
+      <c r="K1133" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1133" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1133" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134971050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>TRVD-G134932485</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>134944901</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>Crime Form Filing 2025-11-0754-CRI</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>26.0001 Commercial Burglary and Theft</t>
+        </is>
+      </c>
+      <c r="J1134" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1134" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P1134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1134" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1134" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134944901</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>TRVD-G134933159</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>134945325</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>CyberRisk Rate/Rule/Form Filing 2025-11-0754-CYB-TCSA</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>05.0003 Commercial Package</t>
+        </is>
+      </c>
+      <c r="J1135" t="inlineStr">
+        <is>
+          <t>Form/Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1135" t="inlineStr">
+        <is>
+          <t>Pending Resubmission</t>
+        </is>
+      </c>
+      <c r="P1135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1135" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1135" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134945325</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>TRVD-G134977960</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>134992221</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>EPL Form Filing 2026-03-0721</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>05.0003 Commercial Package</t>
+        </is>
+      </c>
+      <c r="J1136" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1136" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1136" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1136" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134992221</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>TRVD-G135023927</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>135033042</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>Fiduciary Form Filing 2026-07-0748</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>05.0003 Commercial Package</t>
+        </is>
+      </c>
+      <c r="J1137" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1137" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1137" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1137" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135033042</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>TRVD-G134976745</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>134977564</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>Virginia Manuscript Form Filing 2026-06-0716</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1138" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1138" t="inlineStr">
+        <is>
+          <t>Closed - Approved and Filed</t>
+        </is>
+      </c>
+      <c r="P1138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1138" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1138" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134977564</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>TRVD-G134999313</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>135001093</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>36137</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>Quantum Auto 1.0</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1139" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1139" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1139" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1139" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1139" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135001093</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>TRVD-G135038217</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>135039694</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>38130</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>Quantum Home 2.0</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1140" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1140" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1140" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1140" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1140" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135039694</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>TRVD-G134994138</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>135001104</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>38130</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>Quantum Home 2.0</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1141" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1141" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1141" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1141" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1141" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135001104</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>TRVD-G135001927</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>135003567</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>38130</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>Quantum Home 2.0</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1142" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1142" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1142" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1142" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1142" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135003567</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>TRVD-G135038389</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>135039693</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>38130</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>Quantum Home 2.0</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>30.1000 Dwelling Fire/Personal Liability</t>
+        </is>
+      </c>
+      <c r="J1143" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1143" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1143" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1143" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135039693</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>TRVD-G135027479</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>135028105</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Travelers Personal Security Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>36145</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>Quantum Auto 2.0</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1144" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1144" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1144" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1144" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1144" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135028105</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>TRVD-G134999599</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>135001091</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Travelers Personal Security Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>36145</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>Quantum Auto 2.0</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1145" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1145" t="inlineStr">
+        <is>
+          <t>Pending Response</t>
+        </is>
+      </c>
+      <c r="P1145" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1145" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1145" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135001091</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>TRVD-G134957824</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>134963969</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Travelers Personal Security Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>36145</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>Quantum Auto 2.0</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1146" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1146" t="inlineStr">
+        <is>
+          <t>Closed - Approved and Filed</t>
+        </is>
+      </c>
+      <c r="P1146" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1146" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1146" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134963969</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>TRVD-G134933158</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>134945324</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Company of America</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>25674</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>CyberRisk Rate/Rule/Form Filing 2025-11-0754-CYB-TPCA</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>17.0024 Internet Liability</t>
+        </is>
+      </c>
+      <c r="J1147" t="inlineStr">
+        <is>
+          <t>Form/Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1147" t="inlineStr">
+        <is>
+          <t>Closed - Approved and Filed</t>
+        </is>
+      </c>
+      <c r="P1147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1147" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1147" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134945324</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>TRVD-134997657</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>134997657</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Company of America</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>25674</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>Excess Follow-Form and Umbrella Liability</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1148" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1148" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1148" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1148" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134997657</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>TRVD-134962387</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>134962387</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Company of America</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>25674</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>Travelers Synergy</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>17.2000 Other Liability Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1149" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1149" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1149" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1149" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134962387</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>TRVD-G134999676</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>135001155</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>TAP Automobile</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1150" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1150" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1150" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1150" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1150" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135001155</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>LBPM-135030358</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>135030358</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>23035</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>Homeowners</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1151" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1151" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1151" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1151" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135030358</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>LBPM-134936613</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>134936613</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>23035</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>Personal Automobile</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1152" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1152" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1152" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1152" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1152" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134936613</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>LBPM-134910140</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>134910140</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>23035</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>Personal Property Programs</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>01.0002 Personal Property (Fire and Allied Lines)</t>
+        </is>
+      </c>
+      <c r="J1153" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K1153" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1153" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1153" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134910140</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>LBPM-134912174</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>134912174</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>23035</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>Tuition Programs</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>33.0001 Other Personal Lines</t>
+        </is>
+      </c>
+      <c r="J1154" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1154" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1154" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1154" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134912174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>LBPM-134912105</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>134912105</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>23035</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>Umbrella/Liability Programs</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>17.1000 Other Liability Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1155" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1155" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1155" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1155" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134912105</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>LBPM-134976961</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>134976961</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>23043</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>Homeowners</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1156" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1156" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1156" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1156" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1156" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134976961</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>LBPM-134935811</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>134935811</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>23043</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>Personal Auto</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1157" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1157" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1157" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1157" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1157" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134935811</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>LBPM-134957858</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>134957858</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>12484</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>Homeowners</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1158" t="inlineStr">
+        <is>
+          <t>Form/Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1158" t="inlineStr">
+        <is>
+          <t>Closed - Disapproved and Returned to Company</t>
+        </is>
+      </c>
+      <c r="P1158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1158" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1158" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134957858</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>LWCM-135030616</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>135030616</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1159" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1159" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1159" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1159" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135030616</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>LWCM-134933984</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>134933984</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>17.0022 Other</t>
+        </is>
+      </c>
+      <c r="J1160" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1160" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1160" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1160" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134933984</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>LWCM-134952717</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>134952717</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>Commercial Liability</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>17.0000 Other Liability Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1161" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1161" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1161" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1161" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134952717</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>LBPM-135016955</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>135016955</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>Homeowners</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1162" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1162" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1162" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1162" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1162" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135016955</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>LBRC-134961091</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>134961091</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>General Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>General Insurance</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>24732</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>Businessowners</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1163" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1163" t="inlineStr">
+        <is>
+          <t>Closed - Approved and Filed</t>
+        </is>
+      </c>
+      <c r="P1163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1163" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1163" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134961091</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>LBRC-135001536</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>135001536</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>General Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>General Insurance</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>24732</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>Commercial Auto</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>20.0000 Commercial Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1164" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1164" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1164" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1164" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135001536</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>LBRC-134956488</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>134956488</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>General Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>General Insurance</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>24732</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>Commercial Automobile</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>20.0000 Commercial Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1165" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1165" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1165" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1165" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134956488</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>LBRC-134979825</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>134979825</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>First National Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>First National Insurance</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>24724</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>17.0000 Other Liability Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1166" t="inlineStr">
+        <is>
+          <t>Form/Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1166" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1166" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1166" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134979825</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>LBRC-134981907</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>134981907</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>First National Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>First National Insurance</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>24724</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>Commercial Property</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>01.0001 Commercial Property (Fire and Allied Lines)</t>
+        </is>
+      </c>
+      <c r="J1167" t="inlineStr">
+        <is>
+          <t>Form/Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1167" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1167" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1167" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134981907</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>LWCM-135002384</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>135002384</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>Liberty Insurance</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>42404</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>Commercial Umbrella</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1168" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1168" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1168" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1168" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135002384</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>LWCM-134997509</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>134997509</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>Liberty Insurance</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>42404</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>Commercial Umbrella</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1169" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1169" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P1169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1169" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1169" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134997509</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>LBPM-134912167</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>134912167</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Underwriters Inc.</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Liberty Insurance</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>19917</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>Personal Auto Programs</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1170" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1170" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1170" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1170" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1170" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134912167</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>LINU-134914749</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>134914749</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Underwriters Inc.</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Liberty Insurance</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>19917</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>Pet Health Filing Withdrawal</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>09.0004 Pet Insurance Plans</t>
+        </is>
+      </c>
+      <c r="J1171" t="inlineStr">
+        <is>
+          <t>Form/Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1171" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1171" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1171" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134914749</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>PERR-134915141</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>134915141</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Underwriters Inc.</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>Liberty Insurance</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>19917</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>Pet Insurance</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>09.0004 Pet Insurance Plans</t>
+        </is>
+      </c>
+      <c r="J1172" t="inlineStr">
+        <is>
+          <t>Form/Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1172" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1172" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1172" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134915141</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>GMMX-135038946</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>135038946</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Encompass Independent Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Encompass</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>11251</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>VA_EIIC_Edge_PPA_Form</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1173" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1173" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1173" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1173" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1173" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135038946</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>GMMX-135001630</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>135001630</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Encompass Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Encompass</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>10358</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>VA_EIC_C360_PPA_Form</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1174" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1174" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1174" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1174" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1174" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135001630</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>GMMX-134985899</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>134985899</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Encompass Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Encompass</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>10358</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>VA_EIC_C360_PPA_Rate</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1175" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1175" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1175" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1175" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1175" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134985899</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>GMMX-134952713</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>134952713</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>Encompass Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>Encompass</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>10358</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>VA_EIC_C360_PPA_Rule</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1176" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1176" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1176" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1176" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1176" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134952713</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>FARM-134987243</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>134987243</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>Commercial Businessowners - Artisan Contractors</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1177" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1177" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1177" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1177" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134987243</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>FARM-134987680</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>134987680</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>Commercial Businessowners - BOP ASR</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1178" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1178" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1178" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1178" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134987680</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>FARM-134988030</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>134988030</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>Commercial Businessowners - Habitational</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1179" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1179" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1179" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1179" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134988030</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>FARM-134989623</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>134989623</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>Commercial Businessowners - Real Estate</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1180" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1180" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1180" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1180" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134989623</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>FARM-134988991</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>134988991</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>Commercial Businessowners - Restaurant</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1181" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1181" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1181" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1181" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134988991</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>FARM-134988405</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>134988405</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>Commercial Businessowners - Retail &amp; Service</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1182" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1182" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1182" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1182" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134988405</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>FARM-134988123</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>134988123</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>Commercial Businessowners BOP - MFG</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1183" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1183" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1183" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1183" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134988123</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>FARM-134987920</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>134987920</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>Workers Compensation</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>16.0004 Standard WC</t>
+        </is>
+      </c>
+      <c r="J1184" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1184" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1184" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1184" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134987920</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>FARM-134903432</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>134903432</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>Workers Compensation</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>16.0004 Standard WC</t>
+        </is>
+      </c>
+      <c r="J1185" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1185" t="inlineStr">
+        <is>
+          <t>Closed - Withdrawn</t>
+        </is>
+      </c>
+      <c r="P1185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1185" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1185" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134903432</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>FARM-134988268</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>134988268</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>21660</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>Flex Auto</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1186" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1186" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1186" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1186" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1186" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134988268</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>FARM-134912560</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>134912560</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>21660</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>Flex Auto</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1187" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1187" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1187" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1187" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1187" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134912560</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>FARM-134992701</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>134992701</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>21660</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>Flex Home</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1188" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1188" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1188" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1188" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1188" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134992701</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>FARM-134923350</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>134923350</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>21660</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>Flex Home</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1189" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1189" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1189" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1189" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1189" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134923350</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>FARM-134924387</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>134924387</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>Truck Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Truck Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>21709</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>FSPA</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1190" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1190" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1190" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1190" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1190" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134924387</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>NWPP-G134943024</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>134943245</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>Commercial Package</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>05.0003 Commercial Package</t>
+        </is>
+      </c>
+      <c r="J1191" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1191" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1191" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1191" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134943245</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>NWPP-G134943580</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>134943620</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>Commercial Package</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>05.0003 Commercial Package</t>
+        </is>
+      </c>
+      <c r="J1192" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1192" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1192" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1192" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134943620</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>NWPP-G134930956</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>134931020</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>Commercial Property</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>01.0001 Commercial Property (Fire and Allied Lines)</t>
+        </is>
+      </c>
+      <c r="J1193" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1193" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1193" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1193" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134931020</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>NWPP-G134943626</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>134943682</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>Commercial Property</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>01.0001 Commercial Property (Fire and Allied Lines)</t>
+        </is>
+      </c>
+      <c r="J1194" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1194" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1194" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1194" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134943682</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>NWPP-G135032248</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>135032329</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>Homeowners</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1195" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1195" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1195" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1195" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1195" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135032329</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>NWPP-G135021237</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>135021329</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>Nationwide Agribusiness Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>28223</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>Commercial Package</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>05.0003 Commercial Package</t>
+        </is>
+      </c>
+      <c r="J1196" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1196" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1196" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1196" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135021329</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>NWPP-G135021133</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>135021327</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>Nationwide Agribusiness Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>28223</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>Commercial Property</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>01.0001 Commercial Property (Fire and Allied Lines)</t>
+        </is>
+      </c>
+      <c r="J1197" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1197" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1197" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1197" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135021327</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>NWPP-G134980271</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>134984752</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>Nationwide Agribusiness Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>28223</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>General Liability</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1198" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1198" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1198" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1198" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134984752</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>NWPP-G135037477</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>135037334</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>Nationwide Agribusiness Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>28223</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>General Liability Comm AG Operations</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1199" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1199" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1199" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1199" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135037334</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>NWPP-G134931606</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>134931647</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Nationwide Agribusiness Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>28223</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>Multiline Comm AG Operations</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1200" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1200" t="inlineStr">
+        <is>
+          <t>Closed - Returned to Company</t>
+        </is>
+      </c>
+      <c r="P1200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1200" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1200" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134931647</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>NWPP-G134931607</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>134931648</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>Nationwide Agribusiness Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>28223</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>Multiline Comm AG Operations</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>20.0000 Commercial Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1201" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1201" t="inlineStr">
+        <is>
+          <t>Closed - Withdrawn</t>
+        </is>
+      </c>
+      <c r="P1201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1201" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1201" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134931648</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>NWPP-G134943316</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>134962432</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Nationwide Agribusiness Insurance Company - Farmowners Operations</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>28223</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>Farmowners</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>05.0006 Commercial Farm and Ranch</t>
+        </is>
+      </c>
+      <c r="J1202" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1202" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1202" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1202" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134962432</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>NWPP-G135023919</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>135023937</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>Nationwide General Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>23760</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>Private Passenger Auto</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1203" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1203" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1203" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1203" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1203" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135023937</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>NWPP-G135013654</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>135024061</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Nationwide Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>25453</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>Homeowners</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1204" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1204" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1204" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1204" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1204" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135024061</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>NWPP-G135010443</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>135012454</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Nationwide Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>25453</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>Homeowners, Tenant, Condo</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1205" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1205" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1205" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1205" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1205" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135012454</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>NWPP-G134913164</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>134917954</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Nationwide Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>23787</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>Commercial Umbrella</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1206" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1206" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1206" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1206" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134917954</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>AMLX-134930745</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>134930745</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>American Family Home Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>American Family</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>23450</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>Commercial Automobile</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>20.0000 Commercial Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1207" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1207" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1207" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1207" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134930745</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>AMLX-135027539</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>135027539</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>American Family Home Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>American Family</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>23450</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>Commercial Automobile</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>20.0000 Commercial Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1208" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1208" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1208" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1208" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135027539</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>AMLX-134957893</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>134957893</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>American Family Home Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>American Family</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>23450</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>Community Association Underwriters</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>05.0000 CMP Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1209" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1209" t="inlineStr">
+        <is>
+          <t>Closed - Approved and Filed</t>
+        </is>
+      </c>
+      <c r="P1209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1209" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1209" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134957893</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>AMMH-134939362</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>134939362</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>American Family Home Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>American Family</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>23450</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>Farm &amp; Ranch Program - Commercial Umbrella</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1210" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1210" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1210" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1210" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134939362</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>AMMH-134916931</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>134916931</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>American Family Home Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>American Family</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>23450</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>Farm &amp; Ranch Program - Farmowners</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>05.0006 Commercial Farm and Ranch</t>
+        </is>
+      </c>
+      <c r="J1211" t="inlineStr">
+        <is>
+          <t>Form/Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1211" t="inlineStr">
+        <is>
+          <t>Closed - Approved and Filed</t>
+        </is>
+      </c>
+      <c r="P1211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1211" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1211" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134916931</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>AMMH-134990909</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>134990909</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>American Family Home Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>American Family</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>23450</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>Miscellaneous Fee - Commercial Farmowners</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>05.0006 Commercial Farm and Ranch</t>
+        </is>
+      </c>
+      <c r="J1212" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1212" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1212" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1212" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134990909</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>AMMH-134931300</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>134931300</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>American Family Home Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>American Family</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>23450</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>Miscellaneous Fee - Commercial Farmowners</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>05.0006 Commercial Farm and Ranch</t>
+        </is>
+      </c>
+      <c r="J1213" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1213" t="inlineStr">
+        <is>
+          <t>Closed - Withdrawn</t>
+        </is>
+      </c>
+      <c r="P1213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1213" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1213" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134931300</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>USAA-134914269</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>134914269</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>garrison</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>21253</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>2026 BOP Monoline Fees Withdrawal</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1214" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1214" t="inlineStr">
+        <is>
+          <t>Closed - Approved and Filed</t>
+        </is>
+      </c>
+      <c r="P1214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1214" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1214" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134914269</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>USAA-134914237</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>134914237</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>garrison</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>21253</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>2026 GL Monoline Fees Withdrawal</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1215" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1215" t="inlineStr">
+        <is>
+          <t>Closed - Approved and Filed</t>
+        </is>
+      </c>
+      <c r="P1215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1215" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1215" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134914237</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>USAA-134914246</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>134914246</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>garrison</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>21253</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>2026 IM Monoline Fees Withdrawal</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>09.0005 Other Commercial Inland Marine</t>
+        </is>
+      </c>
+      <c r="J1216" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1216" t="inlineStr">
+        <is>
+          <t>Closed - Approved and Filed</t>
+        </is>
+      </c>
+      <c r="P1216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1216" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1216" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134914246</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>USAA-134969616</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>134977116</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>garrison</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>21253</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1217" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1217" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1217" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1217" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1217" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134977116</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>USAA-134971354</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>134971413</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>garrison</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>21253</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>Personal Auto</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1218" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1218" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1218" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1218" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1218" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134971413</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>GNSC-134930063</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>134930063</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>MGA Insurance Company, Inc.</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>mga insurance</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>40150</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>Personal Auto</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1219" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1219" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P1219" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1219" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1219" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134930063</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>GNSC-135020729</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>135020729</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>MGA Insurance Company, Inc.</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>mga insurance</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>40150</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>Personal Auto</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1220" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1220" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1220" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1220" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1220" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135020729</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>TRVD-G135023046</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>135023154</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>TravCo Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>travco</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>28188</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>Quantum Boat 2.0</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>09.0010 Boatowners/Personal Watercraft</t>
+        </is>
+      </c>
+      <c r="J1221" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1221" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="P1221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1221" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1221" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135023154</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>TRVD-G134933485</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>134936981</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>TravCo Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>travco</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>28188</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>Quantum Boat 2.0</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>09.0010 Boatowners/Personal Watercraft</t>
+        </is>
+      </c>
+      <c r="J1222" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1222" t="inlineStr">
+        <is>
+          <t>Pending Response</t>
+        </is>
+      </c>
+      <c r="P1222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1222" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1222" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134936981</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>TRVD-G135009179</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>135009287</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>TravCo Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>travco</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>28188</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>Quantum Homeowners</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1223" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1223" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1223" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1223" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1223" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135009287</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>USAA-134969586</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>134977138</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>united services</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>25941</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1224" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1224" t="inlineStr">
+        <is>
+          <t>Closed - Filed</t>
+        </is>
+      </c>
+      <c r="P1224" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1224" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1224" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134977138</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>USAA-134971336</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>134971391</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>united services</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>25941</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>Personal Auto</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1225" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1225" t="inlineStr">
+        <is>
+          <t>Response Received</t>
+        </is>
+      </c>
+      <c r="P1225" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1225" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1225" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134971391</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
